--- a/output/pdf_financials_xlsx/NVRO.xlsx
+++ b/output/pdf_financials_xlsx/NVRO.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.486749</v>
+        <v>3.493158</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.13182</v>
+        <v>6.694959</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-2.388765</v>
+        <v>-3.395174</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-4.421529</v>
+        <v>-6.984668</v>
       </c>
     </row>
     <row r="12">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.049141</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.1864</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.049141</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.1864</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09152100000000001</v>
+        <v>0.04238</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.305217</v>
+        <v>0.118817</v>
       </c>
     </row>
     <row r="49">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4350,14 +4350,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-3.493158</v>
+        <v>3.493158</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-6.694959</v>
+        <v>6.694959</v>
       </c>
     </row>
     <row r="81">

--- a/output/pdf_financials_xlsx/NVRO.xlsx
+++ b/output/pdf_financials_xlsx/NVRO.xlsx
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.749464</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.809268</v>
       </c>
     </row>
     <row r="111">
@@ -2920,7 +2920,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3000,7 +3004,11 @@
           <t>Interest and accretion expense 9, 11</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.749464</v>
       </c>
@@ -3872,7 +3880,11 @@
           <t>Finder's warrants fair value - Private Placement</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -4536,7 +4548,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
